--- a/test_outputs/Test_Cases_Executed_01-06-2026_to_30-06-2026.xlsx
+++ b/test_outputs/Test_Cases_Executed_01-06-2026_to_30-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN\OmniBizAI\test_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FEC619-41FA-4CC7-B9F5-8E928568EB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A75156C-19A1-472F-9C90-ED650B1805C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -2080,19 +2080,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2404,16 +2404,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2516,18 +2516,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2977,18 +2977,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3498,18 +3498,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4190,16 +4190,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -4469,7 +4469,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
@@ -4479,19 +4479,19 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="13"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -5001,18 +5001,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5442,18 +5442,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5903,18 +5903,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6364,18 +6364,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6909,18 +6909,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7510,18 +7510,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
